--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Proposta por vendedor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34312594-F862-4DA2-A907-65B34044E731}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F3E65D-B90F-4399-A13F-EC76C8462F75}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
@@ -890,11 +890,21 @@
       </c>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
+      <c r="U3" s="6">
+        <v>44</v>
+      </c>
+      <c r="V3" s="6">
+        <v>46</v>
+      </c>
+      <c r="W3" s="6">
+        <v>47</v>
+      </c>
+      <c r="X3" s="6">
+        <v>51</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>55</v>
+      </c>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="6"/>
@@ -952,11 +962,21 @@
       </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
+      <c r="U4" s="6">
+        <v>17</v>
+      </c>
+      <c r="V4" s="6">
+        <v>18</v>
+      </c>
+      <c r="W4" s="6">
+        <v>24</v>
+      </c>
+      <c r="X4" s="6">
+        <v>28</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>30</v>
+      </c>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="6"/>
@@ -1014,11 +1034,21 @@
       </c>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
+      <c r="U5" s="6">
+        <v>46</v>
+      </c>
+      <c r="V5" s="6">
+        <v>48</v>
+      </c>
+      <c r="W5" s="6">
+        <v>50</v>
+      </c>
+      <c r="X5" s="6">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>52</v>
+      </c>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="6"/>
@@ -1076,11 +1106,21 @@
       </c>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
+      <c r="U6" s="6">
+        <v>23</v>
+      </c>
+      <c r="V6" s="6">
+        <v>24</v>
+      </c>
+      <c r="W6" s="6">
+        <v>24</v>
+      </c>
+      <c r="X6" s="6">
+        <v>24</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>25</v>
+      </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="6"/>
@@ -1138,11 +1178,21 @@
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
+      <c r="U7" s="6">
+        <v>22</v>
+      </c>
+      <c r="V7" s="6">
+        <v>22</v>
+      </c>
+      <c r="W7" s="6">
+        <v>23</v>
+      </c>
+      <c r="X7" s="6">
+        <v>25</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>28</v>
+      </c>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
       <c r="AB7" s="6"/>
@@ -1200,11 +1250,21 @@
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
+      <c r="U8" s="6">
+        <v>12</v>
+      </c>
+      <c r="V8" s="6">
+        <v>12</v>
+      </c>
+      <c r="W8" s="6">
+        <v>12</v>
+      </c>
+      <c r="X8" s="6">
+        <v>12</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>12</v>
+      </c>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
       <c r="AB8" s="6"/>
@@ -1262,11 +1322,21 @@
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
+      <c r="U9" s="6">
+        <v>20</v>
+      </c>
+      <c r="V9" s="6">
+        <v>21</v>
+      </c>
+      <c r="W9" s="6">
+        <v>21</v>
+      </c>
+      <c r="X9" s="6">
+        <v>28</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>32</v>
+      </c>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
       <c r="AB9" s="6"/>
@@ -1324,11 +1394,21 @@
       </c>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
+      <c r="U10" s="6">
+        <v>2</v>
+      </c>
+      <c r="V10" s="6">
+        <v>2</v>
+      </c>
+      <c r="W10" s="6">
+        <v>2</v>
+      </c>
+      <c r="X10" s="6">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>2</v>
+      </c>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
       <c r="AB10" s="6"/>
@@ -1386,11 +1466,21 @@
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
+      <c r="U11" s="6">
+        <v>22</v>
+      </c>
+      <c r="V11" s="6">
+        <v>24</v>
+      </c>
+      <c r="W11" s="6">
+        <v>25</v>
+      </c>
+      <c r="X11" s="6">
+        <v>25</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>26</v>
+      </c>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
       <c r="AB11" s="6"/>
@@ -1448,11 +1538,21 @@
       </c>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
+      <c r="U12" s="6">
+        <v>34</v>
+      </c>
+      <c r="V12" s="6">
+        <v>34</v>
+      </c>
+      <c r="W12" s="6">
+        <v>38</v>
+      </c>
+      <c r="X12" s="6">
+        <v>40</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>41</v>
+      </c>
       <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
       <c r="AB12" s="6"/>
